--- a/www/download/COUNTRY.DEU.rpA2.xlsx
+++ b/www/download/COUNTRY.DEU.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.731925086265228</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.769088761654336</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.885386722112306</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.898408000431061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.938262378454218</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>1.08271977276317</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>1.11656986865627</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1.05752964164908</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>0.884017010217504</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.803923182782427</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.803793923582443</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.796432000106346</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.72966072452248</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074648032</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948695538313</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37.601</t>
+          <t>0.897467953611551</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.498</t>
+          <t>1.03361990466554</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.463</t>
+          <t>1.27382102974805</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.911</t>
+          <t>1.20803313206082</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>38.424</t>
+          <t>1.17654262209657</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>1.07594301253671</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>39.316</t>
+          <t>1.10964549498394</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.096</t>
+          <t>1.04201669489696</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>38.726</t>
+          <t>0.797973098720595</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>0.801321138352967</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>38.835</t>
+          <t>0.860461776404146</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>39.075</t>
+          <t>0.808229569602605</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>39.724</t>
+          <t>0.768122144958874</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>0.852854925078645</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>0.90065231573066</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33.852</t>
+          <t>0.201987770343302</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33.756</t>
+          <t>0.30102911125288</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.647</t>
+          <t>0.465417669824157</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.046</t>
+          <t>0.418684605422473</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.567</t>
+          <t>0.358394387987123</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.229</t>
+          <t>0.301439073555613</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.333</t>
+          <t>0.319407450659395</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>0.311715124701403</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34.653</t>
+          <t>0.16198053776098</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34.658</t>
+          <t>0.127160582684103</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>0.178221691857977</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>34.684</t>
+          <t>0.188572669397674</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>35.288</t>
+          <t>0.181217762761364</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>35.843</t>
+          <t>0.234673904893349</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35.862</t>
+          <t>0.263944090174338</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>57679.197</t>
+          <t>-0.297428940424942</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56921.734</t>
+          <t>-0.223287000750746</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56526.422</t>
+          <t>-0.11538249871824</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56997.003</t>
+          <t>-0.154618172819389</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>57318.04</t>
+          <t>-0.191835834458761</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>57658.023</t>
+          <t>-0.216409621752422</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57334.344</t>
+          <t>-0.212332657461404</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>-0.229932477926873</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>-0.332111329530524</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>-0.294863370744315</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>-0.293657003851195</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>-0.288659204134167</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>-0.309326505044399</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>57721.711</t>
+          <t>-0.258226054796062</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>56739.567</t>
+          <t>-0.214605278910174</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>49333.493</t>
+          <t>217114155249.432</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48495.041</t>
+          <t>202955072855.684</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47917.779</t>
+          <t>193594077457.872</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48296.046</t>
+          <t>203347302830.098</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48623.541</t>
+          <t>206046838351.455</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>48867.203</t>
+          <t>215921190355.215</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>48588.388</t>
+          <t>208941315272.587</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>205271809618.251</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>218813389779.73</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>228615368076.517</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>225157274336.421</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>235766389053.453</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>246112141785.387</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>225290925384.694</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>46952.701</t>
+          <t>195647766136.699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>110748975647.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>100594602484.196</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>88321151466.2556</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>93114403085.2604</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>96756279269.6339</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>101299830660.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>99647304015.2165</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>100373513848.545</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>113191634584.611</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>115575898389.784</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>109369407941.3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>110046093039.782</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>114022097563.148</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>110874689927.222</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>105582480743.811</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>2090915.55394235</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>2049271.47081113</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>2212348.99014684</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>2273224.80970465</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>2385109.59641337</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>2721895.11872437</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>2652885.5386178</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>2534408.96493498</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>2244643.00325704</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>2075899.42221553</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>54.99</t>
+          <t>2002602.90011232</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>1937395.45700913</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>1737225.21520885</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>1397615.59225702</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>1463598.36195738</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>412789.072454636</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>397093.10281528</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>384248.683699003</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>392268.505876131</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>399842.534928399</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>398464.654351489</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>380323.507574583</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>380781.104942649</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>413039.578600048</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>456185.373197423</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>471550.977078345</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>485573.68534775</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>552044.313623887</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>608739.929270972</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>557551.341923293</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>947084.366490825</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>882616.740907669</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>828028.323375597</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>859024.066239171</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>898055.144550991</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>946460.618162972</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>883495.026759544</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>879137.208171044</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>44.28</t>
+          <t>1003350.01911137</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>1136984.9334222</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>1191076.8778607</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>1298067.41011083</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>1519036.07128753</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>1519009.37603552</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>1219286.80717446</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>0.378132642556137</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.69</t>
+          <t>0.48801794126004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>0.672867062316342</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.22</t>
+          <t>0.640386219629592</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>0.584072307198068</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.514632369052465</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>0.541105509924911</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>0.521749964484292</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>0.358662387258665</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>0.355117928126402</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>0.396090541227027</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>0.382394339124414</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>0.363679349453728</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>0.437829694917139</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>0.48853232479938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>545091.443710321</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>534115.768423765</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>481628.808970487</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>487508.218568299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>475748.678829375</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>431506.788696572</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>420795.060472542</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>446076.710621606</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>524492.793947102</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>585167.597490354</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>584756.219184891</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>591668.458139547</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>669238.552231181</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.731925086265228</t>
+          <t>3271.5637376675</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769088761654336</t>
+          <t>2980.05102749723</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885386722112306</t>
+          <t>2624.93391583962</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898408000431061</t>
+          <t>2734.95867606357</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262378454218</t>
+          <t>2799.09391239141</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977276317</t>
+          <t>2875.46710551251</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986865627</t>
+          <t>2820.23332338654</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964164908</t>
+          <t>2860.21468237384</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017010217504</t>
+          <t>3266.43103294408</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182782427</t>
+          <t>3334.75383431774</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923582443</t>
+          <t>3171.9665876247</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432000106346</t>
+          <t>3172.82011993374</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.72966072452248</t>
+          <t>3231.18616989198</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074648032</t>
+          <t>3093.34291011415</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695538313</t>
+          <t>2944.14992463801</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>104844259040.621</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>97156551610.5033</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>84049048399.9061</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>92643563408.175</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>96947293357.4817</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>101259194443.307</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>107318681181.246</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.068</t>
+          <t>121289065999.634</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>142965085166.137</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>158121320881.401</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>153969686543.345</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>161026035923.677</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>176470777526.396</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>177099855289.852</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>153787783421.199</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>109343318579.027</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>101677424928.282</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>88251352778.7275</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>97503983699.4927</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.302</t>
+          <t>103418119765.774</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>107131268781.154</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>113913152351.145</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>123582137880.233</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>147508094235.971</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>162362469363.638</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>158215920423.276</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>163484872646.109</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.876</t>
+          <t>178514651343.45</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>178324224241.8</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>153582715743.356</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.512</t>
+          <t>-4499059538.40548</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.276</t>
+          <t>-4520873317.7787</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.367</t>
+          <t>-4202304378.82143</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7.401</t>
+          <t>-4860420291.31769</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.184</t>
+          <t>-6470826408.29278</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>-5872074337.84759</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.311</t>
+          <t>-6594471169.89968</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.739</t>
+          <t>-2293071880.59927</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8.105</t>
+          <t>-4543009069.83354</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9.144</t>
+          <t>-4241148482.23729</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>-4246233879.93122</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.438</t>
+          <t>-2458836722.43256</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.884</t>
+          <t>-2043873817.05374</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1224368951.9475</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205067677.843087</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4508.64877908255</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.148</t>
+          <t>4434.36939478629</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.708</t>
+          <t>4391.16548856515</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.767</t>
+          <t>4486.38852347108</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>4433.96715186593</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.399</t>
+          <t>4355.27555415484</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>4346.27711394484</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>4352.53159131984</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>4437.97698503559</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.871</t>
+          <t>4518.98470677223</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>4428.35255007101</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5.362</t>
+          <t>4386.08857285645</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>4406.30185412219</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6.788</t>
+          <t>4447.70029272353</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5.914</t>
+          <t>4382.46233187934</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>4718.64914841948</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>4654.00757260685</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.959</t>
+          <t>4621.12003158654</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.979</t>
+          <t>4720.01000024144</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>4667.78943229179</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>4590.31098072045</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.706</t>
+          <t>4575.20310718142</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.828</t>
+          <t>4573.87818808356</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>4661.59989234861</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>4744.84046266935</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>4658.44324234364</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>4606.63774406312</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.989</t>
+          <t>4620.85292074961</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.272</t>
+          <t>4658.45852567967</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.986</t>
+          <t>4618.99772050676</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>89.75</t>
+          <t>577907.20701724</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>103.36</t>
+          <t>581114.496989226</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>127.38</t>
+          <t>569372.66299253</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>120.8</t>
+          <t>600858.480607013</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>117.65</t>
+          <t>600302.862251976</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>107.59</t>
+          <t>614536.849060768</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>110.96</t>
+          <t>636044.31902115</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>695201.351947121</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>839065.950346315</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>1007507.32754731</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>1095999.9529517</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>1258715.0600739</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>1510355.82197752</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>1671979.62800848</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>1265888.36750474</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>41938361990.6655</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>41168362314.7562</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>42225172317.0788</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>46127034954.7566</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>47705161430.1857</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>54275110580.3002</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>55024559095.0653</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>56001719306.3508</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>60709715943.9797</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>67419095037.8096</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>69874258694.3873</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>77556579966.0622</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>83652632733.8926</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>79282791955.3295</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>62743422598.9202</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-29.74</t>
+          <t>504027.545040582</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-22.33</t>
+          <t>498306.496186612</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>483107.582522955</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-15.46</t>
+          <t>510269.044784054</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>520999.817854744</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>548615.686679205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>543158.262380266</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-22.99</t>
+          <t>547031.874859046</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-33.21</t>
+          <t>670655.969606237</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>789020.360184291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-29.37</t>
+          <t>865640.065505454</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-28.87</t>
+          <t>1003709.30337883</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-30.93</t>
+          <t>1170974.86363347</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>1323009.70758408</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-21.46</t>
+          <t>1004959.19095404</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>177425.927</t>
+          <t>125536497055.719</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>174515.976</t>
+          <t>115017827016.712</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>173121.02</t>
+          <t>103691273484.436</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>178940.299</t>
+          <t>113532023567.575</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>179355.141</t>
+          <t>121707697630.933</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>179683.133</t>
+          <t>136046352586.445</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>179878.685</t>
+          <t>133252143950.48</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>178820.342</t>
+          <t>130966912224.559</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>180525.117</t>
+          <t>153809862801.567</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>184479.397</t>
+          <t>165559869913.255</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>180910.643</t>
+          <t>164945052884.057</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>180004.37</t>
+          <t>178660965475.585</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>183558.761</t>
+          <t>189322801586.842</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>188436.315</t>
+          <t>190537805859.072</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>188684.981</t>
+          <t>161628628591.949</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>152626.778</t>
+          <t>73879.6619766577</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>149686.573</t>
+          <t>82808.0008026142</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>147749.545</t>
+          <t>86265.0804695758</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>152743.584</t>
+          <t>90589.4358229591</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>153268.943</t>
+          <t>79303.0443972323</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>153432.002</t>
+          <t>65921.1623815622</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>153567.009</t>
+          <t>92886.0566408838</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>152743.391</t>
+          <t>148169.477088074</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>153789.216</t>
+          <t>168409.980740078</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>156618.972</t>
+          <t>218486.967363019</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>152689.596</t>
+          <t>230359.88744625</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>152127.096</t>
+          <t>255005.756695061</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>155489.58</t>
+          <t>339380.958344055</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>159418.922</t>
+          <t>348969.920424398</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>157162.936</t>
+          <t>260929.176550695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>217114.155</t>
+          <t>-83598135065.0537</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>202955.073</t>
+          <t>-73849464701.9555</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>193594.077</t>
+          <t>-61466101167.3568</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>203347.303</t>
+          <t>-67404988612.8186</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>206046.838</t>
+          <t>-74002536200.7471</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>215921.19</t>
+          <t>-81771242006.1446</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>208941.315</t>
+          <t>-78227584855.4146</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>205271.81</t>
+          <t>-74965192918.2083</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>218813.39</t>
+          <t>-93100146857.5878</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>228615.368</t>
+          <t>-98140774875.4457</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>225157.274</t>
+          <t>-95070794189.6692</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>235766.389</t>
+          <t>-101104385509.523</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>246112.142</t>
+          <t>-105670168852.95</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>225290.925</t>
+          <t>-111255013903.742</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>195647.766</t>
+          <t>-98885205993.0285</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>1056023.36682</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>1007321.96497</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>890469.64307</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>897064.59083</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>862328.08299</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>768933.95974</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>758537.39575</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>805528.24857</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>961033.54614</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1094768.77747</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1105569.44245</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1168674.7893</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1341856.5192</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1447149.57748</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1255690.97522</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>94629.744</t>
+          <t>0.0212558615807381</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>91310.368</t>
+          <t>0.020677897962817</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>89837.832</t>
+          <t>0.021772737439555</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>92857.402</t>
+          <t>0.0223277681371954</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>91738.565</t>
+          <t>0.02104990949854</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>90903.901</t>
+          <t>0.017205134338401</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>89944.246</t>
+          <t>0.0200974746917341</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>88909.474</t>
+          <t>0.0225876770416037</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>90076.831</t>
+          <t>0.0248159113602402</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>91725.918</t>
+          <t>0.0286209786496833</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>89140.453</t>
+          <t>0.0321675624073745</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>88194.152</t>
+          <t>0.0387971000529059</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>89441.463</t>
+          <t>0.0407694859493459</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>90284.882</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>89465.148</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1363254.26397007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>1310121.86457592</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>1142969.47780482</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>1150434.99498854</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1130675.20037073</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>1017493.19579972</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1005060.25879547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>1068159.18640789</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1281841.85530205</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>1415296.91437412</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>1406878.01531334</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>1443676.29595017</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1617724.45786562</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>1809250.3412473</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>1734712.46695596</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>110748.976</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>100594.602</t>
+          <t>1502412.29547561</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>88321.151</t>
+          <t>1317411.14858811</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>93114.403</t>
+          <t>1326358.61866775</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>96756.279</t>
+          <t>1302406.93863858</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>101299.831</t>
+          <t>1172559.80554357</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>99647.304</t>
+          <t>1158039.93511591</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>100373.514</t>
+          <t>1229729.51173504</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>113191.635</t>
+          <t>1479553.94155057</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>115575.898</t>
+          <t>1638875.00976356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>109369.408</t>
+          <t>1637759.62104069</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>110046.093</t>
+          <t>1677285.14398029</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>114022.098</t>
+          <t>1875703.64141804</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>110874.69</t>
+          <t>2097001.03153539</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>105582.481</t>
+          <t>2017691.93984275</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>8511749.96256924</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>8276300.33663781</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>67.29</t>
+          <t>7366901.39568792</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>64.04</t>
+          <t>7401377.1805815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>7184357.139993</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>6412025.09902104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>6310558.6501231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>6738992.81156657</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>8104710.03110398</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>9144246.35647392</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>9183339.8407178</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>9437534.09870476</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>36.37</t>
+          <t>10884321.7521092</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.049</t>
+          <t>1565823.16105272</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>1574515.97314039</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>1595825.50331131</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.385</t>
+          <t>1633583.99896788</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.722</t>
+          <t>1711168.19227524</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.653</t>
+          <t>1722289.03455401</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.534</t>
+          <t>1709599.1639397</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>1698931.65152834</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>1698284.98947203</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>1692748.03649668</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.937</t>
+          <t>1718338.36227257</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1746733.59539946</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1812032.68718169</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1812740.50663989</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1363254.26397007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1366629.34788592</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1367887.27938545</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1385840.64218068</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1418319.0540482</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1487220.49170109</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1498136.42213078</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1487260.39086597</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1473349.9808319</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1466778.69985087</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1452908.41558482</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1479614.55459368</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1510272.60285515</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1567941.67538722</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1559966.69082129</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>726016.022724546</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>705252.26229439</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>642026.418801891</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>652764.452152251</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>626978.746431417</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>541826.541906429</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>547621.353234095</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>598294.903834961</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>725618.559679428</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>846884.877226439</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>880161.876619309</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>957817.412819707</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1112986.75497196</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1175234.90225461</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>968030.770867249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>152626778469.503</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>149686573290.406</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>147749545193.752</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>152743583670.096</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>153268942538.549</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>153432002497.321</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>153567009267.013</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>152743391134.187</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>153789216462.438</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>156618971967.312</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>152689595926.448</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>152127096060.953</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>155489579828.264</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>159418921592.089</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>157162935519.671</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>177425926629.721</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>174515975957.612</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>173121019743.326</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>178940299119.153</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>179355141146.38</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>179683133029.321</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>179878685361.945</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>178820341641.315</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>180525117431.092</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>184479397188.585</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>180910643316.415</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>180004369849.266</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>183558761423.858</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>188436315064.82</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>188684981102.741</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>94629743593.2316</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>91310368223.3416</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>89837832034.3608</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>92857401544.4347</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>91738564898.06</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>90903901156.5486</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>89944245858.607</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>88909473690.2631</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>90076831200.654</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>91725918206.0993</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>89140453217.7088</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>88194151953.974</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>89441462881.9583</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>90284881810.2775</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>89465147914.2947</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37601000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>37498000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>37463000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>37911000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>38424000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39144000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39316000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39096000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>38726000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>38880000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>38835000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>39075000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>39724000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40450357.994188</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>40849767.096668</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>33852000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>33756000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>33647000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>34046000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>34567000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35229000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35333000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35093000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>34653000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>34658000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>34480000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>34684000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>35288000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>35843000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>35861788.1040119</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>57679196738.1535</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>56921734359.5757</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>56526421658.4249</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>56997003030.2113</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>57318039756.847</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>57658022765.4988</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>57334343544.1498</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5.651e+10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5.5724e+10</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5.6044e+10</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5.5693e+10</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5.5862e+10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>5.6788e+10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>57721710897.5781</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>56739567063.1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>49333493412.3921</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>48495041184.2737</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>47917778993.4606</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48296045892.6359</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>48623541304.493</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>48867203486.7267</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>48588388114.2661</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4.7915e+10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4.7126e+10</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4.7259e+10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4.6689e+10</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4.6883e+10</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4.7776e+10</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4.841e+10</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>46952701355.6198</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.292360206508077</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.294446300408508</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.296502004060942</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.309167344856546</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.300709474163641</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.302691879989424</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.307297726488227</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.318450369437362</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.337570238433673</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.341056812054553</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.339734656467144</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.338469540174099</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.337491902506053</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.347081543739561</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.36261815887713</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.59454138680484</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.595258406339624</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.594653617929654</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.584727948123357</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.588371699399295</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.583821059901513</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.578503908321464</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.569470000808505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.550528974734686</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.560057982965693</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.549858319779674</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.55309471873137</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.557789083181953</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.555608619892097</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.54494562514477</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.113098406687083</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.110295293251868</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.108844378009404</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.106104707020097</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.110918826437064</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.113487060109063</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.114198365190309</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.112079629754133</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.111900786831642</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0988852049797545</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.110407023753181</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.108435741094531</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.104719014311994</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0973098363683425</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0924362159780996</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.393819180663955</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.395025210109739</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.39659801633945</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.41299369341765</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.410432331257694</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.410506960143121</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.416300607079038</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.423331044584821</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.442806197211773</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.450157894154631</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.446913876649963</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.438678513111825</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.431780702172936</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.439531299891024</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.456494261196427</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.547261397238165</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.546883703646024</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.54577213163059</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.532162925542613</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.532423285583175</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.530032853522447</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.524471762274684</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.51952664534938</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.502607174425204</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.497517869906896</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.495829042218748</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.503949097689891</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.51417188019682</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.509340315695164</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.494468677090216</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0589194220978801</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0580910862442375</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0576298520299602</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0548433810397368</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0571443831591306</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0594601863344323</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0592276306462776</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0571423100657985</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0545866283630233</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0523242359384732</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0572570811312892</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0573723891982841</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0540474176302441</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0511283844138118</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0490370617133568</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4289714.99955</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4148350.8472</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3708413.41752</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3767286.13336</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3737973.56792</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3399402.20853</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3373850.6568</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3534860.73441</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4292179.88478</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4871137.04873</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5034337.63434</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5362002.02775</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>6161850.08853</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6788492.30254</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>5913505.46421</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2283990.57679</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2207664.55777</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1959437.56739</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1979123.07082</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1929385.68507</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1714386.34745</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1705661.28835</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1828024.41557</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2205172.50123</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2485759.88699</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2517921.49766</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2635102.5568</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2988690.39639</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3272235.93379</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2985722.71071</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6229963.21060905</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6404784.34412815</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6577082.45551666</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6759822.08704437</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6956322.46315011</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7155973.14476165</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7327014.06849413</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7460931.2845158</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7586839.43485666</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7701435.24330397</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7833162.16535079</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8009309.99162415</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>8201285.55467841</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
